--- a/DateBase/orders/Dang Nguyen 195_2026-6-7.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-6-7.xlsx
@@ -990,6 +990,9 @@
       <c r="G2" t="str">
         <v>0582031051010851561055135155555551551010151510510105100125755010025015070130100101051030303015102020</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
